--- a/MR_UKBiobank/BinaryData/SA_Birth/gMR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Birth/gMR_dat.xlsx
@@ -392,7 +392,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.05726215776995249</v>
@@ -434,7 +434,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -552,7 +552,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.08974742432906892</v>
@@ -594,7 +594,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -712,7 +712,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.09492350715161053</v>
@@ -754,7 +754,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -960,7 +960,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.026283757462650763</v>
@@ -1002,7 +1002,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -1120,7 +1120,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.036256525969759784</v>
@@ -1162,7 +1162,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -1280,7 +1280,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.027715522113857877</v>
@@ -1322,7 +1322,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -1528,7 +1528,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.03308404396808673</v>
@@ -1570,7 +1570,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -1688,7 +1688,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>-0.0014405541548894829</v>
@@ -1730,7 +1730,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -1848,7 +1848,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.007085011142868088</v>
@@ -1890,7 +1890,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -2096,7 +2096,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.011314011507970068</v>
@@ -2138,7 +2138,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -2256,7 +2256,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.012593826648729236</v>
@@ -2298,7 +2298,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -2416,7 +2416,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.012435535141960727</v>
@@ -2458,7 +2458,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -2664,7 +2664,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0011258129354349156</v>
@@ -2706,7 +2706,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -2824,7 +2824,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.013753209139866914</v>
@@ -2866,7 +2866,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -2984,7 +2984,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>0.009436626976586279</v>
@@ -3026,7 +3026,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>
@@ -3232,7 +3232,7 @@
         <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>0.039983</v>
+        <v>0.042572</v>
       </c>
       <c r="H3" t="n">
         <v>0.009671836986219455</v>
@@ -3274,7 +3274,7 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0069265306122449</v>
+        <v>0.0144209183673469</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
@@ -3392,7 +3392,7 @@
         <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.066314</v>
+        <v>0.080535</v>
       </c>
       <c r="H5" t="n">
         <v>0.010231018951813855</v>
@@ -3434,7 +3434,7 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0114775510204082</v>
+        <v>0.0282632653061224</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
@@ -3552,7 +3552,7 @@
         <v>39</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060792</v>
+        <v>0.071191</v>
       </c>
       <c r="H7" t="n">
         <v>-0.0071835024744593004</v>
@@ -3594,7 +3594,7 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0113857142857143</v>
+        <v>0.0245357142857143</v>
       </c>
       <c r="V7" t="s">
         <v>43</v>

--- a/MR_UKBiobank/BinaryData/SA_Birth/gMR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Birth/gMR_dat.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="52">
   <si>
     <t>SNP</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>exposure</t>
+  </si>
+  <si>
+    <t>beta.exposure_corrected</t>
+  </si>
+  <si>
+    <t>se.exposure_corrected</t>
   </si>
   <si>
     <t>action</t>
@@ -291,28 +297,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.05446618875587519</v>
@@ -324,16 +336,16 @@
         <v>0.38618231955977006</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O2" t="n">
         <v>0.01402717502790013</v>
@@ -345,7 +357,7 @@
         <v>325648.0</v>
       </c>
       <c r="R2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -357,42 +369,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.05726215776995249</v>
@@ -404,16 +422,16 @@
         <v>0.28559364712818747</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O3" t="n">
         <v>0.011672976356314325</v>
@@ -425,7 +443,7 @@
         <v>325648.0</v>
       </c>
       <c r="R3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -434,45 +452,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>0.0793845755854418</v>
@@ -484,16 +508,16 @@
         <v>0.4161272294010711</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O4" t="n">
         <v>0.01592154796470022</v>
@@ -505,7 +529,7 @@
         <v>325648.0</v>
       </c>
       <c r="R4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -517,42 +541,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.08974742432906892</v>
@@ -564,16 +594,16 @@
         <v>0.07151586989632978</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O5" t="n">
         <v>0.017093467311994133</v>
@@ -585,7 +615,7 @@
         <v>325648.0</v>
       </c>
       <c r="R5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -594,45 +624,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.05130229650856274</v>
@@ -644,16 +680,16 @@
         <v>0.2553063430452513</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O6" t="n">
         <v>0.011593277255414043</v>
@@ -665,7 +701,7 @@
         <v>325648.0</v>
       </c>
       <c r="R6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -677,42 +713,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.09492350715161053</v>
@@ -724,16 +766,16 @@
         <v>0.07840521053407361</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O7" t="n">
         <v>0.016461533380336443</v>
@@ -745,7 +787,7 @@
         <v>325648.0</v>
       </c>
       <c r="R7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -754,21 +796,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -859,28 +907,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.02529405969538345</v>
@@ -892,16 +946,16 @@
         <v>0.3861763531976298</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O2" t="n">
         <v>0.014681899284066368</v>
@@ -913,7 +967,7 @@
         <v>325710.0</v>
       </c>
       <c r="R2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -925,42 +979,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.026283757462650763</v>
@@ -972,16 +1032,16 @@
         <v>0.28559608240459305</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O3" t="n">
         <v>0.012528526252695373</v>
@@ -993,7 +1053,7 @@
         <v>325710.0</v>
       </c>
       <c r="R3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1002,45 +1062,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.02137471960785234</v>
@@ -1052,16 +1118,16 @@
         <v>0.41612937889533635</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O4" t="n">
         <v>0.016473902544292388</v>
@@ -1073,7 +1139,7 @@
         <v>325710.0</v>
       </c>
       <c r="R4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1085,42 +1151,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.036256525969759784</v>
@@ -1132,16 +1204,16 @@
         <v>0.07151914279573854</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O5" t="n">
         <v>0.017486155423678505</v>
@@ -1153,7 +1225,7 @@
         <v>325710.0</v>
       </c>
       <c r="R5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1162,45 +1234,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.03332481235349933</v>
@@ -1212,16 +1290,16 @@
         <v>0.25530686807282554</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O6" t="n">
         <v>0.01238624551734081</v>
@@ -1233,7 +1311,7 @@
         <v>325710.0</v>
       </c>
       <c r="R6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1245,42 +1323,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.027715522113857877</v>
@@ -1292,16 +1376,16 @@
         <v>0.07840256670043905</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O7" t="n">
         <v>0.01686894587374536</v>
@@ -1313,7 +1397,7 @@
         <v>325710.0</v>
       </c>
       <c r="R7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1322,21 +1406,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1427,28 +1517,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.01727794604451405</v>
@@ -1460,16 +1556,16 @@
         <v>0.38618464298220284</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O2" t="n">
         <v>0.018460485271897344</v>
@@ -1481,7 +1577,7 @@
         <v>325558.0</v>
       </c>
       <c r="R2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -1493,42 +1589,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.03308404396808673</v>
@@ -1540,16 +1642,16 @@
         <v>0.2855942719884014</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O3" t="n">
         <v>0.015741001717552036</v>
@@ -1561,7 +1663,7 @@
         <v>325558.0</v>
       </c>
       <c r="R3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -1570,45 +1672,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.024370764061687335</v>
@@ -1620,16 +1728,16 @@
         <v>0.4161424385209394</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O4" t="n">
         <v>0.020645891525153566</v>
@@ -1641,7 +1749,7 @@
         <v>325558.0</v>
       </c>
       <c r="R4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -1653,42 +1761,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>-0.0014405541548894829</v>
@@ -1700,16 +1814,16 @@
         <v>0.07151567462633386</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O5" t="n">
         <v>0.022211576262700188</v>
@@ -1721,7 +1835,7 @@
         <v>325558.0</v>
       </c>
       <c r="R5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -1730,45 +1844,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.023742129733722587</v>
@@ -1780,16 +1900,16 @@
         <v>0.2553093458001339</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
         <v>0.01554980599249952</v>
@@ -1801,7 +1921,7 @@
         <v>325558.0</v>
       </c>
       <c r="R6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -1813,42 +1933,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.007085011142868088</v>
@@ -1860,16 +1986,16 @@
         <v>0.07840077651294086</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
         <v>0.021308685404993713</v>
@@ -1881,7 +2007,7 @@
         <v>325558.0</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -1890,21 +2016,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -1995,28 +2127,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.004043020218607174</v>
@@ -2028,16 +2166,16 @@
         <v>0.38617586648368346</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O2" t="n">
         <v>0.028975132224539953</v>
@@ -2049,7 +2187,7 @@
         <v>325713.0</v>
       </c>
       <c r="R2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2061,42 +2199,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.011314011507970068</v>
@@ -2108,16 +2252,16 @@
         <v>0.2855965220915346</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O3" t="n">
         <v>0.02448205053344941</v>
@@ -2129,7 +2273,7 @@
         <v>325713.0</v>
       </c>
       <c r="R3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2138,45 +2282,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.0010224074135774179</v>
@@ -2188,16 +2338,16 @@
         <v>0.4161301513909485</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
         <v>0.032476512562888055</v>
@@ -2209,7 +2359,7 @@
         <v>325713.0</v>
       </c>
       <c r="R4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2221,42 +2371,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.012593826648729236</v>
@@ -2268,16 +2424,16 @@
         <v>0.07152001915797036</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O5" t="n">
         <v>0.034530448940129806</v>
@@ -2289,7 +2445,7 @@
         <v>325713.0</v>
       </c>
       <c r="R5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2298,45 +2454,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.012899288005024916</v>
@@ -2348,16 +2510,16 @@
         <v>0.255307586740474</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O6" t="n">
         <v>0.024251088353309927</v>
@@ -2369,7 +2531,7 @@
         <v>325713.0</v>
       </c>
       <c r="R6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2381,42 +2543,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.012435535141960727</v>
@@ -2428,16 +2596,16 @@
         <v>0.07840491475624246</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O7" t="n">
         <v>0.03348432846199588</v>
@@ -2449,7 +2617,7 @@
         <v>325713.0</v>
       </c>
       <c r="R7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -2458,21 +2626,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -2563,28 +2737,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>0.00513801660068689</v>
@@ -2596,16 +2776,16 @@
         <v>0.3861889140696408</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O2" t="n">
         <v>0.0067228023379815255</v>
@@ -2617,7 +2797,7 @@
         <v>319468.0</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -2629,42 +2809,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>-0.0011258129354349156</v>
@@ -2676,16 +2862,16 @@
         <v>0.2855872888677426</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O3" t="n">
         <v>0.005686990803263278</v>
@@ -2697,7 +2883,7 @@
         <v>319468.0</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -2706,45 +2892,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.005479769427927969</v>
@@ -2756,16 +2948,16 @@
         <v>0.41612774988418244</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O4" t="n">
         <v>0.007529667581937513</v>
@@ -2777,7 +2969,7 @@
         <v>319468.0</v>
       </c>
       <c r="R4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -2789,42 +2981,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.013753209139866914</v>
@@ -2836,16 +3034,16 @@
         <v>0.07143594976648679</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O5" t="n">
         <v>0.008015314338261569</v>
@@ -2857,7 +3055,7 @@
         <v>319468.0</v>
       </c>
       <c r="R5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -2866,45 +3064,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>-0.0018838366394349788</v>
@@ -2916,16 +3120,16 @@
         <v>0.25529943531120486</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O6" t="n">
         <v>0.005629979945460021</v>
@@ -2937,7 +3141,7 @@
         <v>319468.0</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -2949,42 +3153,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>0.009436626976586279</v>
@@ -2996,16 +3206,16 @@
         <v>0.07831144277361113</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O7" t="n">
         <v>0.007722480434781245</v>
@@ -3017,7 +3227,7 @@
         <v>319468.0</v>
       </c>
       <c r="R7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3026,21 +3236,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -3131,28 +3347,34 @@
       <c r="Z1" t="s">
         <v>24</v>
       </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>39</v>
       </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.063746</v>
+        <v>0.063746</v>
       </c>
       <c r="H2" t="n">
         <v>-0.018503533066584518</v>
@@ -3164,16 +3386,16 @@
         <v>0.3863477335684914</v>
       </c>
       <c r="K2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O2" t="n">
         <v>0.01767756174861193</v>
@@ -3185,7 +3407,7 @@
         <v>312981.0</v>
       </c>
       <c r="R2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S2" t="n">
         <v>2.1E-8</v>
@@ -3197,42 +3419,48 @@
         <v>0.0113683673469388</v>
       </c>
       <c r="V2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X2" t="n">
+        <v>0.063746</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0113683673469388</v>
+      </c>
+      <c r="Z2" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z2" t="e">
+      <c r="AA2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
         <v>39</v>
       </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042572</v>
+        <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
         <v>0.009671836986219455</v>
@@ -3244,16 +3472,16 @@
         <v>0.2855141366408824</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O3" t="n">
         <v>0.015036907334755144</v>
@@ -3265,7 +3493,7 @@
         <v>312981.0</v>
       </c>
       <c r="R3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S3" t="n">
         <v>8.03E-9</v>
@@ -3274,45 +3502,51 @@
         <v>49371.0</v>
       </c>
       <c r="U3" t="n">
+        <v>0.0069265306122449</v>
+      </c>
+      <c r="V3" t="s">
+        <v>45</v>
+      </c>
+      <c r="W3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-0.042572</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.0144209183673469</v>
       </c>
-      <c r="V3" t="s">
-        <v>43</v>
-      </c>
-      <c r="W3" t="s">
-        <v>43</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3" t="e">
+      <c r="AA3" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB3" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.041722</v>
+        <v>0.041722</v>
       </c>
       <c r="H4" t="n">
         <v>-0.04159828723565264</v>
@@ -3324,16 +3558,16 @@
         <v>0.41622654410331617</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O4" t="n">
         <v>0.01967321528235143</v>
@@ -3345,7 +3579,7 @@
         <v>312981.0</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S4" t="n">
         <v>1.11E-9</v>
@@ -3357,42 +3591,48 @@
         <v>0.00684234693877551</v>
       </c>
       <c r="V4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
+        <v>0.041722</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.00684234693877551</v>
+      </c>
+      <c r="Z4" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" t="e">
+      <c r="AA4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" t="s">
         <v>40</v>
       </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.080535</v>
+        <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
         <v>0.010231018951813855</v>
@@ -3404,16 +3644,16 @@
         <v>0.07139411018560232</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O5" t="n">
         <v>0.021202947077213662</v>
@@ -3425,7 +3665,7 @@
         <v>312981.0</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S5" t="n">
         <v>7.76E-9</v>
@@ -3434,45 +3674,51 @@
         <v>49372.0</v>
       </c>
       <c r="U5" t="n">
+        <v>0.0114775510204082</v>
+      </c>
+      <c r="V5" t="s">
+        <v>45</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X5" t="n">
+        <v>-0.080535</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.0282632653061224</v>
       </c>
-      <c r="V5" t="s">
-        <v>43</v>
-      </c>
-      <c r="W5" t="s">
-        <v>43</v>
-      </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z5" t="e">
+      <c r="AA5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB5" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>0.036955</v>
+        <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
         <v>0.005637822740121491</v>
@@ -3484,16 +3730,16 @@
         <v>0.25520558755962824</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O6" t="n">
         <v>0.014877914491965133</v>
@@ -3505,7 +3751,7 @@
         <v>312981.0</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S6" t="n">
         <v>2.72E-7</v>
@@ -3517,42 +3763,48 @@
         <v>0.00718163265306122</v>
       </c>
       <c r="V6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="W6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="X6" t="n">
+        <v>-0.036955</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.00718163265306122</v>
+      </c>
+      <c r="Z6" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z6" t="e">
+      <c r="AA6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB6" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
         <v>39</v>
       </c>
-      <c r="E7" t="s">
-        <v>37</v>
-      </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G7" t="n">
-        <v>0.071191</v>
+        <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
         <v>-0.0071835024744593004</v>
@@ -3564,16 +3816,16 @@
         <v>0.07827312201060128</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="O7" t="n">
         <v>0.020516769712278324</v>
@@ -3585,7 +3837,7 @@
         <v>312981.0</v>
       </c>
       <c r="R7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="S7" t="n">
         <v>9.54E-8</v>
@@ -3594,21 +3846,27 @@
         <v>49372.0</v>
       </c>
       <c r="U7" t="n">
+        <v>0.0113857142857143</v>
+      </c>
+      <c r="V7" t="s">
+        <v>45</v>
+      </c>
+      <c r="W7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.071191</v>
+      </c>
+      <c r="Y7" t="n">
         <v>0.0245357142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>43</v>
-      </c>
-      <c r="W7" t="s">
-        <v>43</v>
-      </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>2.0</v>
       </c>
-      <c r="Y7" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z7" t="e">
+      <c r="AA7" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB7" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/MR_UKBiobank/BinaryData/SA_Birth/gMR_dat.xlsx
+++ b/MR_UKBiobank/BinaryData/SA_Birth/gMR_dat.xlsx
@@ -70,6 +70,12 @@
     <t>outcome</t>
   </si>
   <si>
+    <t>cases.outcome</t>
+  </si>
+  <si>
+    <t>controls.outcome</t>
+  </si>
+  <si>
     <t>pval.exposure</t>
   </si>
   <si>
@@ -83,12 +89,6 @@
   </si>
   <si>
     <t>exposure</t>
-  </si>
-  <si>
-    <t>beta.exposure_corrected</t>
-  </si>
-  <si>
-    <t>se.exposure_corrected</t>
   </si>
   <si>
     <t>action</t>
@@ -327,13 +327,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05446618875587519</v>
+        <v>0.05388465006091829</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38618231955977006</v>
+        <v>0.5424429318810526</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -348,37 +348,37 @@
         <v>44</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01402717502790013</v>
+        <v>0.016295749785091705</v>
       </c>
       <c r="P2" t="n">
-        <v>1.032158802400024E-4</v>
+        <v>9.4412392462399E-4</v>
       </c>
       <c r="Q2" t="n">
-        <v>325648.0</v>
+        <v>242561.0</v>
       </c>
       <c r="R2" t="s">
         <v>44</v>
       </c>
       <c r="S2" t="n">
+        <v>22031.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -413,13 +413,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.05726215776995249</v>
+        <v>-0.05598910574557157</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28559364712818747</v>
+        <v>0.3472281199368406</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -434,37 +434,37 @@
         <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>0.011672976356314325</v>
+        <v>0.013567186208159072</v>
       </c>
       <c r="P3" t="n">
-        <v>9.31744998977341E-7</v>
+        <v>3.678411254605508E-5</v>
       </c>
       <c r="Q3" t="n">
-        <v>325648.0</v>
+        <v>242561.0</v>
       </c>
       <c r="R3" t="s">
         <v>44</v>
       </c>
       <c r="S3" t="n">
+        <v>22031.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -499,13 +499,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0793845755854418</v>
+        <v>0.06067947464411199</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161272294010711</v>
+        <v>0.6018341777944517</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -520,37 +520,37 @@
         <v>44</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01592154796470022</v>
+        <v>0.018399526318854123</v>
       </c>
       <c r="P4" t="n">
-        <v>6.16474030027964E-7</v>
+        <v>9.7416913467362E-4</v>
       </c>
       <c r="Q4" t="n">
-        <v>325648.0</v>
+        <v>242561.0</v>
       </c>
       <c r="R4" t="s">
         <v>44</v>
       </c>
       <c r="S4" t="n">
+        <v>22031.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -585,13 +585,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.08974742432906892</v>
+        <v>-0.07279997612383104</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07151586989632978</v>
+        <v>0.07389893676229897</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -606,37 +606,37 @@
         <v>44</v>
       </c>
       <c r="O5" t="n">
-        <v>0.017093467311994133</v>
+        <v>0.01977669545931851</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5177489238497393E-7</v>
+        <v>2.3223070234656187E-4</v>
       </c>
       <c r="Q5" t="n">
-        <v>325648.0</v>
+        <v>242561.0</v>
       </c>
       <c r="R5" t="s">
         <v>44</v>
       </c>
       <c r="S5" t="n">
+        <v>22031.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -671,13 +671,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.05130229650856274</v>
+        <v>-0.04621700371128947</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553063430452513</v>
+        <v>0.30237136225526773</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -692,37 +692,37 @@
         <v>44</v>
       </c>
       <c r="O6" t="n">
-        <v>0.011593277255414043</v>
+        <v>0.013475777813755746</v>
       </c>
       <c r="P6" t="n">
-        <v>9.636352327297116E-6</v>
+        <v>6.04392946716859E-4</v>
       </c>
       <c r="Q6" t="n">
-        <v>325648.0</v>
+        <v>242561.0</v>
       </c>
       <c r="R6" t="s">
         <v>44</v>
       </c>
       <c r="S6" t="n">
+        <v>22031.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -757,13 +757,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.09492350715161053</v>
+        <v>-0.08110370622327319</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840521053407361</v>
+        <v>0.08128264642708433</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -778,37 +778,37 @@
         <v>44</v>
       </c>
       <c r="O7" t="n">
-        <v>0.016461533380336443</v>
+        <v>0.019065581383366247</v>
       </c>
       <c r="P7" t="n">
-        <v>8.099086265747901E-9</v>
+        <v>2.1004815348838648E-5</v>
       </c>
       <c r="Q7" t="n">
-        <v>325648.0</v>
+        <v>242561.0</v>
       </c>
       <c r="R7" t="s">
         <v>44</v>
       </c>
       <c r="S7" t="n">
+        <v>22031.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>220530.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -937,13 +937,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.02529405969538345</v>
+        <v>-0.02913429902640263</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861763531976298</v>
+        <v>0.5424359338996954</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -958,37 +958,37 @@
         <v>47</v>
       </c>
       <c r="O2" t="n">
-        <v>0.014681899284066368</v>
+        <v>0.01712151375389113</v>
       </c>
       <c r="P2" t="n">
-        <v>0.08492366862734163</v>
+        <v>0.08882674864014324</v>
       </c>
       <c r="Q2" t="n">
-        <v>325710.0</v>
+        <v>242601.0</v>
       </c>
       <c r="R2" t="s">
         <v>47</v>
       </c>
       <c r="S2" t="n">
+        <v>19188.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -1023,13 +1023,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.026283757462650763</v>
+        <v>0.018211722436741115</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.28559608240459305</v>
+        <v>0.3472368209529227</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -1044,37 +1044,37 @@
         <v>47</v>
       </c>
       <c r="O3" t="n">
-        <v>0.012528526252695373</v>
+        <v>0.014601917960898252</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03591283588355619</v>
+        <v>0.21231889203771392</v>
       </c>
       <c r="Q3" t="n">
-        <v>325710.0</v>
+        <v>242601.0</v>
       </c>
       <c r="R3" t="s">
         <v>47</v>
       </c>
       <c r="S3" t="n">
+        <v>19188.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -1109,13 +1109,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.02137471960785234</v>
+        <v>-0.02138788773991447</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41612937889533635</v>
+        <v>0.6018318143783414</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -1130,37 +1130,37 @@
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>0.016473902544292388</v>
+        <v>0.01921624525285811</v>
       </c>
       <c r="P4" t="n">
-        <v>0.19446273141300288</v>
+        <v>0.26570380814281475</v>
       </c>
       <c r="Q4" t="n">
-        <v>325710.0</v>
+        <v>242601.0</v>
       </c>
       <c r="R4" t="s">
         <v>47</v>
       </c>
       <c r="S4" t="n">
+        <v>19188.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -1195,13 +1195,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.036256525969759784</v>
+        <v>0.035893362755746276</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07151914279573854</v>
+        <v>0.07390117930264097</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -1216,37 +1216,37 @@
         <v>47</v>
       </c>
       <c r="O5" t="n">
-        <v>0.017486155423678505</v>
+        <v>0.020445464442048318</v>
       </c>
       <c r="P5" t="n">
-        <v>0.038131180131115536</v>
+        <v>0.07916253756044188</v>
       </c>
       <c r="Q5" t="n">
-        <v>325710.0</v>
+        <v>242601.0</v>
       </c>
       <c r="R5" t="s">
         <v>47</v>
       </c>
       <c r="S5" t="n">
+        <v>19188.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -1281,13 +1281,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.03332481235349933</v>
+        <v>0.036783837770900496</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25530686807282554</v>
+        <v>0.30237509326012674</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -1302,37 +1302,37 @@
         <v>47</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01238624551734081</v>
+        <v>0.01444918918700389</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00713516161673343</v>
+        <v>0.01090472635097333</v>
       </c>
       <c r="Q6" t="n">
-        <v>325710.0</v>
+        <v>242601.0</v>
       </c>
       <c r="R6" t="s">
         <v>47</v>
       </c>
       <c r="S6" t="n">
+        <v>19188.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -1367,13 +1367,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.027715522113857877</v>
+        <v>0.023813276031314543</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840256670043905</v>
+        <v>0.0812795495484355</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -1388,37 +1388,37 @@
         <v>47</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01686894587374536</v>
+        <v>0.019749072282960897</v>
       </c>
       <c r="P7" t="n">
-        <v>0.10038484611363935</v>
+        <v>0.2278976488613782</v>
       </c>
       <c r="Q7" t="n">
-        <v>325710.0</v>
+        <v>242601.0</v>
       </c>
       <c r="R7" t="s">
         <v>47</v>
       </c>
       <c r="S7" t="n">
+        <v>19188.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>223413.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -1547,13 +1547,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.01727794604451405</v>
+        <v>-0.03320177085099953</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38618464298220284</v>
+        <v>0.5424314527602403</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -1568,37 +1568,37 @@
         <v>48</v>
       </c>
       <c r="O2" t="n">
-        <v>0.018460485271897344</v>
+        <v>0.021673254252391493</v>
       </c>
       <c r="P2" t="n">
-        <v>0.34930298023377815</v>
+        <v>0.12554127563951162</v>
       </c>
       <c r="Q2" t="n">
-        <v>325558.0</v>
+        <v>242497.0</v>
       </c>
       <c r="R2" t="s">
         <v>48</v>
       </c>
       <c r="S2" t="n">
+        <v>11941.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -1633,13 +1633,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03308404396808673</v>
+        <v>0.02352266048288492</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855942719884014</v>
+        <v>0.34724347105325015</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -1654,37 +1654,37 @@
         <v>48</v>
       </c>
       <c r="O3" t="n">
-        <v>0.015741001717552036</v>
+        <v>0.018519397541186162</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03557298962653082</v>
+        <v>0.2040264407765686</v>
       </c>
       <c r="Q3" t="n">
-        <v>325558.0</v>
+        <v>242497.0</v>
       </c>
       <c r="R3" t="s">
         <v>48</v>
       </c>
       <c r="S3" t="n">
+        <v>11941.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -1719,13 +1719,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.024370764061687335</v>
+        <v>-0.03796788724627567</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161424385209394</v>
+        <v>0.6018280638523363</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -1740,37 +1740,37 @@
         <v>48</v>
       </c>
       <c r="O4" t="n">
-        <v>0.020645891525153566</v>
+        <v>0.02422711222744447</v>
       </c>
       <c r="P4" t="n">
-        <v>0.23783435139778358</v>
+        <v>0.11707608173122236</v>
       </c>
       <c r="Q4" t="n">
-        <v>325558.0</v>
+        <v>242497.0</v>
       </c>
       <c r="R4" t="s">
         <v>48</v>
       </c>
       <c r="S4" t="n">
+        <v>11941.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -1805,13 +1805,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0014405541548894829</v>
+        <v>-0.004442221257288936</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07151567462633386</v>
+        <v>0.07390606894105907</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -1826,37 +1826,37 @@
         <v>48</v>
       </c>
       <c r="O5" t="n">
-        <v>0.022211576262700188</v>
+        <v>0.02626985792258301</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9482886478015347</v>
+        <v>0.8657183357664503</v>
       </c>
       <c r="Q5" t="n">
-        <v>325558.0</v>
+        <v>242497.0</v>
       </c>
       <c r="R5" t="s">
         <v>48</v>
       </c>
       <c r="S5" t="n">
+        <v>11941.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -1891,13 +1891,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.023742129733722587</v>
+        <v>0.03188817331174147</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2553093458001339</v>
+        <v>0.302385184146608</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -1912,37 +1912,37 @@
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01554980599249952</v>
+        <v>0.018314534243821914</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1267997794151316</v>
+        <v>0.08165899200325857</v>
       </c>
       <c r="Q6" t="n">
-        <v>325558.0</v>
+        <v>242497.0</v>
       </c>
       <c r="R6" t="s">
         <v>48</v>
       </c>
       <c r="S6" t="n">
+        <v>11941.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -1977,13 +1977,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.007085011142868088</v>
+        <v>-0.006051131325099106</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840077651294086</v>
+        <v>0.08128554167680425</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -1998,37 +1998,37 @@
         <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>0.021308685404993713</v>
+        <v>0.025288072723451873</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7395162306656686</v>
+        <v>0.810882301077914</v>
       </c>
       <c r="Q7" t="n">
-        <v>325558.0</v>
+        <v>242497.0</v>
       </c>
       <c r="R7" t="s">
         <v>48</v>
       </c>
       <c r="S7" t="n">
+        <v>11941.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>230556.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -2157,13 +2157,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004043020218607174</v>
+        <v>-0.002670610378128303</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.38617586648368346</v>
+        <v>0.5424335230809182</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -2178,37 +2178,37 @@
         <v>49</v>
       </c>
       <c r="O2" t="n">
-        <v>0.028975132224539953</v>
+        <v>0.03393279935796385</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8890280782880872</v>
+        <v>0.937268923217305</v>
       </c>
       <c r="Q2" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R2" t="s">
         <v>49</v>
       </c>
       <c r="S2" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -2243,13 +2243,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.011314011507970068</v>
+        <v>-0.005112389771452084</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855965220915346</v>
+        <v>0.34723808032052367</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -2264,37 +2264,37 @@
         <v>49</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02448205053344941</v>
+        <v>0.028706929827034523</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6439845391994117</v>
+        <v>0.8586530438635547</v>
       </c>
       <c r="Q3" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R3" t="s">
         <v>49</v>
       </c>
       <c r="S3" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -2329,13 +2329,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0010224074135774179</v>
+        <v>0.017548934407431355</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4161301513909485</v>
+        <v>0.6018309748848942</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -2350,37 +2350,37 @@
         <v>49</v>
       </c>
       <c r="O4" t="n">
-        <v>0.032476512562888055</v>
+        <v>0.038309574418154246</v>
       </c>
       <c r="P4" t="n">
-        <v>0.974885592758964</v>
+        <v>0.6468933814347281</v>
       </c>
       <c r="Q4" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R4" t="s">
         <v>49</v>
       </c>
       <c r="S4" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -2415,13 +2415,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.012593826648729236</v>
+        <v>0.03773955013033292</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07152001915797036</v>
+        <v>0.0739026310474314</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -2436,37 +2436,37 @@
         <v>49</v>
       </c>
       <c r="O5" t="n">
-        <v>0.034530448940129806</v>
+        <v>0.04020503707625095</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7153229937219523</v>
+        <v>0.3478965220969526</v>
       </c>
       <c r="Q5" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R5" t="s">
         <v>49</v>
       </c>
       <c r="S5" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -2501,13 +2501,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.012899288005024916</v>
+        <v>0.014623204439896067</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.255307586740474</v>
+        <v>0.3023767224642729</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -2522,37 +2522,37 @@
         <v>49</v>
       </c>
       <c r="O6" t="n">
-        <v>0.024251088353309927</v>
+        <v>0.02843989295568158</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5947914269845959</v>
+        <v>0.6071266341536696</v>
       </c>
       <c r="Q6" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R6" t="s">
         <v>49</v>
       </c>
       <c r="S6" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -2587,13 +2587,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.012435535141960727</v>
+        <v>0.008450432318288167</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07840491475624246</v>
+        <v>0.08128300144680815</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -2608,37 +2608,37 @@
         <v>49</v>
       </c>
       <c r="O7" t="n">
-        <v>0.03348432846199588</v>
+        <v>0.03905631859051631</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7103517344513429</v>
+        <v>0.8287030076467559</v>
       </c>
       <c r="Q7" t="n">
-        <v>325713.0</v>
+        <v>242603.0</v>
       </c>
       <c r="R7" t="s">
         <v>49</v>
       </c>
       <c r="S7" t="n">
+        <v>4950.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>237653.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -2767,13 +2767,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00513801660068689</v>
+        <v>-0.0019225124352504283</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3861889140696408</v>
+        <v>0.5423636982187633</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -2788,37 +2788,37 @@
         <v>50</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0067228023379815255</v>
+        <v>0.007830726136541533</v>
       </c>
       <c r="P2" t="n">
-        <v>0.44470809117663945</v>
+        <v>0.8060624696880728</v>
       </c>
       <c r="Q2" t="n">
-        <v>319468.0</v>
+        <v>238093.0</v>
       </c>
       <c r="R2" t="s">
         <v>50</v>
       </c>
       <c r="S2" t="n">
+        <v>92788.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -2853,13 +2853,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0011258129354349156</v>
+        <v>0.0016158261905173897</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855872888677426</v>
+        <v>0.3472151638225399</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -2874,37 +2874,37 @@
         <v>50</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005686990803263278</v>
+        <v>0.006633441659905971</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8430741260099764</v>
+        <v>0.8075499926684905</v>
       </c>
       <c r="Q3" t="n">
-        <v>319468.0</v>
+        <v>238093.0</v>
       </c>
       <c r="R3" t="s">
         <v>50</v>
       </c>
       <c r="S3" t="n">
+        <v>92788.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -2939,13 +2939,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.005479769427927969</v>
+        <v>-0.010020181438103534</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41612774988418244</v>
+        <v>0.6018929577938033</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -2960,37 +2960,37 @@
         <v>50</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007529667581937513</v>
+        <v>0.008775031603545104</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4667622585995815</v>
+        <v>0.2534968748715</v>
       </c>
       <c r="Q4" t="n">
-        <v>319468.0</v>
+        <v>238093.0</v>
       </c>
       <c r="R4" t="s">
         <v>50</v>
       </c>
       <c r="S4" t="n">
+        <v>92788.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -3025,13 +3025,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.013753209139866914</v>
+        <v>0.014557206367567441</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07143594976648679</v>
+        <v>0.07384719416362513</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -3046,37 +3046,37 @@
         <v>50</v>
       </c>
       <c r="O5" t="n">
-        <v>0.008015314338261569</v>
+        <v>0.00936583939173569</v>
       </c>
       <c r="P5" t="n">
-        <v>0.08618648440736683</v>
+        <v>0.12011587231081126</v>
       </c>
       <c r="Q5" t="n">
-        <v>319468.0</v>
+        <v>238093.0</v>
       </c>
       <c r="R5" t="s">
         <v>50</v>
       </c>
       <c r="S5" t="n">
+        <v>92788.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -3111,13 +3111,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0018838366394349788</v>
+        <v>-0.0022304526266393168</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25529943531120486</v>
+        <v>0.3023587421721764</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -3132,37 +3132,37 @@
         <v>50</v>
       </c>
       <c r="O6" t="n">
-        <v>0.005629979945460021</v>
+        <v>0.006567368150203291</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7379207678201551</v>
+        <v>0.7341377768867239</v>
       </c>
       <c r="Q6" t="n">
-        <v>319468.0</v>
+        <v>238093.0</v>
       </c>
       <c r="R6" t="s">
         <v>50</v>
       </c>
       <c r="S6" t="n">
+        <v>92788.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -3197,13 +3197,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.009436626976586279</v>
+        <v>0.01204706471771405</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07831144277361113</v>
+        <v>0.08123296358985775</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -3218,37 +3218,37 @@
         <v>50</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007722480434781245</v>
+        <v>0.009018568178826111</v>
       </c>
       <c r="P7" t="n">
-        <v>0.22171958125750224</v>
+        <v>0.18161242913618258</v>
       </c>
       <c r="Q7" t="n">
-        <v>319468.0</v>
+        <v>238093.0</v>
       </c>
       <c r="R7" t="s">
         <v>50</v>
       </c>
       <c r="S7" t="n">
+        <v>92788.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>145305.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
@@ -3377,13 +3377,13 @@
         <v>0.063746</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.018503533066584518</v>
+        <v>-0.019510958055327828</v>
       </c>
       <c r="I2" t="n">
         <v>0.6624</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3863477335684914</v>
+        <v>0.5425878529874517</v>
       </c>
       <c r="K2" t="s">
         <v>43</v>
@@ -3398,37 +3398,37 @@
         <v>51</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01767756174861193</v>
+        <v>0.020720272050528867</v>
       </c>
       <c r="P2" t="n">
-        <v>0.29522676282649435</v>
+        <v>0.3463789339534049</v>
       </c>
       <c r="Q2" t="n">
-        <v>312981.0</v>
+        <v>233259.0</v>
       </c>
       <c r="R2" t="s">
         <v>51</v>
       </c>
       <c r="S2" t="n">
+        <v>13165.0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>220094.0</v>
+      </c>
+      <c r="U2" t="n">
         <v>2.1E-8</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>14009.0</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.0113683673469388</v>
       </c>
-      <c r="V2" t="s">
-        <v>45</v>
-      </c>
-      <c r="W2" t="s">
-        <v>45</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.063746</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.0113683673469388</v>
+      <c r="X2" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>45</v>
       </c>
       <c r="Z2" t="n">
         <v>2.0</v>
@@ -3463,13 +3463,13 @@
         <v>-0.039983</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009671836986219455</v>
+        <v>0.029544522431526006</v>
       </c>
       <c r="I3" t="n">
         <v>0.3171</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2855141366408824</v>
+        <v>0.34716559704019995</v>
       </c>
       <c r="K3" t="s">
         <v>43</v>
@@ -3484,37 +3484,37 @@
         <v>51</v>
       </c>
       <c r="O3" t="n">
-        <v>0.015036907334755144</v>
+        <v>0.017646060099163967</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5200900968259594</v>
+        <v>0.09407472686666186</v>
       </c>
       <c r="Q3" t="n">
-        <v>312981.0</v>
+        <v>233259.0</v>
       </c>
       <c r="R3" t="s">
         <v>51</v>
       </c>
       <c r="S3" t="n">
+        <v>13165.0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>220094.0</v>
+      </c>
+      <c r="U3" t="n">
         <v>8.03E-9</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>49371.0</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.0069265306122449</v>
       </c>
-      <c r="V3" t="s">
-        <v>45</v>
-      </c>
-      <c r="W3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-0.042572</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.0144209183673469</v>
+      <c r="X3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>45</v>
       </c>
       <c r="Z3" t="n">
         <v>2.0</v>
@@ -3549,13 +3549,13 @@
         <v>0.041722</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.04159828723565264</v>
+        <v>-0.046784216152794045</v>
       </c>
       <c r="I4" t="n">
         <v>0.6699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.41622654410331617</v>
+        <v>0.6019188970200506</v>
       </c>
       <c r="K4" t="s">
         <v>43</v>
@@ -3570,37 +3570,37 @@
         <v>51</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01967321528235143</v>
+        <v>0.023026106779093114</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03447573552661242</v>
+        <v>0.04217490828963671</v>
       </c>
       <c r="Q4" t="n">
-        <v>312981.0</v>
+        <v>233259.0</v>
       </c>
       <c r="R4" t="s">
         <v>51</v>
       </c>
       <c r="S4" t="n">
+        <v>13165.0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>220094.0</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.11E-9</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.00684234693877551</v>
       </c>
-      <c r="V4" t="s">
-        <v>45</v>
-      </c>
-      <c r="W4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0.041722</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.00684234693877551</v>
+      <c r="X4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
       </c>
       <c r="Z4" t="n">
         <v>2.0</v>
@@ -3635,13 +3635,13 @@
         <v>-0.066314</v>
       </c>
       <c r="H5" t="n">
-        <v>0.010231018951813855</v>
+        <v>0.02249888155601091</v>
       </c>
       <c r="I5" t="n">
         <v>0.0882</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07139411018560232</v>
+        <v>0.07381923098358477</v>
       </c>
       <c r="K5" t="s">
         <v>43</v>
@@ -3656,37 +3656,37 @@
         <v>51</v>
       </c>
       <c r="O5" t="n">
-        <v>0.021202947077213662</v>
+        <v>0.024782083845225927</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6294308019766125</v>
+        <v>0.3639475256498252</v>
       </c>
       <c r="Q5" t="n">
-        <v>312981.0</v>
+        <v>233259.0</v>
       </c>
       <c r="R5" t="s">
         <v>51</v>
       </c>
       <c r="S5" t="n">
+        <v>13165.0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>220094.0</v>
+      </c>
+      <c r="U5" t="n">
         <v>7.76E-9</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.0114775510204082</v>
       </c>
-      <c r="V5" t="s">
-        <v>45</v>
-      </c>
-      <c r="W5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-0.080535</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.0282632653061224</v>
+      <c r="X5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>45</v>
       </c>
       <c r="Z5" t="n">
         <v>2.0</v>
@@ -3721,13 +3721,13 @@
         <v>-0.036955</v>
       </c>
       <c r="H6" t="n">
-        <v>0.005637822740121491</v>
+        <v>0.012903392917920713</v>
       </c>
       <c r="I6" t="n">
         <v>0.2786</v>
       </c>
       <c r="J6" t="n">
-        <v>0.25520558755962824</v>
+        <v>0.30229701747842525</v>
       </c>
       <c r="K6" t="s">
         <v>43</v>
@@ -3742,37 +3742,37 @@
         <v>51</v>
       </c>
       <c r="O6" t="n">
-        <v>0.014877914491965133</v>
+        <v>0.01743825293805133</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7047331273653274</v>
+        <v>0.4593318072556323</v>
       </c>
       <c r="Q6" t="n">
-        <v>312981.0</v>
+        <v>233259.0</v>
       </c>
       <c r="R6" t="s">
         <v>51</v>
       </c>
       <c r="S6" t="n">
+        <v>13165.0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>220094.0</v>
+      </c>
+      <c r="U6" t="n">
         <v>2.72E-7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.00718163265306122</v>
       </c>
-      <c r="V6" t="s">
-        <v>45</v>
-      </c>
-      <c r="W6" t="s">
-        <v>45</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.036955</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.00718163265306122</v>
+      <c r="X6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
       </c>
       <c r="Z6" t="n">
         <v>2.0</v>
@@ -3807,13 +3807,13 @@
         <v>-0.060792</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0071835024744593004</v>
+        <v>0.0019179349812824909</v>
       </c>
       <c r="I7" t="n">
         <v>0.0886</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07827312201060128</v>
+        <v>0.08114799428960941</v>
       </c>
       <c r="K7" t="s">
         <v>43</v>
@@ -3828,37 +3828,37 @@
         <v>51</v>
       </c>
       <c r="O7" t="n">
-        <v>0.020516769712278324</v>
+        <v>0.024020125187544483</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7262423848414066</v>
+        <v>0.9363589415298127</v>
       </c>
       <c r="Q7" t="n">
-        <v>312981.0</v>
+        <v>233259.0</v>
       </c>
       <c r="R7" t="s">
         <v>51</v>
       </c>
       <c r="S7" t="n">
+        <v>13165.0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>220094.0</v>
+      </c>
+      <c r="U7" t="n">
         <v>9.54E-8</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>49372.0</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.0113857142857143</v>
       </c>
-      <c r="V7" t="s">
-        <v>45</v>
-      </c>
-      <c r="W7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-0.071191</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.0245357142857143</v>
+      <c r="X7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>45</v>
       </c>
       <c r="Z7" t="n">
         <v>2.0</v>
